--- a/DiplomovkaOpravene.xlsx
+++ b/DiplomovkaOpravene.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Diplomovka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5DAF2A-711F-4877-B190-11B0C55A680E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63765CAC-B5BC-488F-AA9C-3BAFBECF4563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10682" uniqueCount="1237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10696" uniqueCount="1237">
   <si>
     <t>Token</t>
   </si>
@@ -3756,15 +3756,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -3774,6 +3767,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3829,24 +3841,25 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normálna" xfId="0" builtinId="0"/>
@@ -4126,7 +4139,7 @@
         <v>16</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -4329,7 +4342,7 @@
         <v>33</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -4532,7 +4545,7 @@
         <v>45</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -4850,8 +4863,8 @@
       <c r="H27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>17</v>
+      <c r="I27" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5750,7 +5763,7 @@
         <v>45</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6123,6 +6136,12 @@
       <c r="G71" s="2">
         <v>6</v>
       </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
@@ -6179,7 +6198,7 @@
         <v>45</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6204,6 +6223,12 @@
       <c r="G74" s="2">
         <v>4</v>
       </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
@@ -6608,7 +6633,7 @@
         <v>45</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7230,6 +7255,9 @@
       <c r="C110" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D110" t="s">
+        <v>17</v>
+      </c>
       <c r="E110" s="2" t="s">
         <v>13</v>
       </c>
@@ -7243,7 +7271,7 @@
         <v>45</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7459,6 +7487,9 @@
       <c r="C118" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D118" t="s">
+        <v>17</v>
+      </c>
       <c r="E118" s="2" t="s">
         <v>13</v>
       </c>
@@ -7588,7 +7619,7 @@
         <v>45</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7617,7 +7648,7 @@
         <v>45</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7936,7 +7967,7 @@
         <v>30</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8226,7 +8257,7 @@
         <v>16</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8503,6 +8534,9 @@
       <c r="D154" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="E154" t="s">
+        <v>17</v>
+      </c>
       <c r="F154" s="2" t="s">
         <v>14</v>
       </c>
@@ -8571,7 +8605,7 @@
         <v>45</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8787,6 +8821,9 @@
       <c r="C164" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D164" t="s">
+        <v>17</v>
+      </c>
       <c r="E164" s="2" t="s">
         <v>13</v>
       </c>
@@ -8800,7 +8837,7 @@
         <v>33</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8874,8 +8911,8 @@
       <c r="D167" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E167" s="2" t="s">
-        <v>16</v>
+      <c r="E167" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>32</v>
@@ -9016,6 +9053,9 @@
       <c r="C172" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D172" t="s">
+        <v>17</v>
+      </c>
       <c r="E172" s="2" t="s">
         <v>13</v>
       </c>
@@ -9029,7 +9069,7 @@
         <v>45</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9116,7 +9156,7 @@
         <v>45</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9260,6 +9300,9 @@
       <c r="H180" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="I180" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="181" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
@@ -9954,7 +9997,7 @@
         <v>45</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10244,7 +10287,7 @@
         <v>45</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10273,7 +10316,7 @@
         <v>45</v>
       </c>
       <c r="I215" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10705,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="H230" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I230" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I230" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="231" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10734,10 +10777,10 @@
         <v>4</v>
       </c>
       <c r="H231" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I231" t="s">
         <v>106</v>
-      </c>
-      <c r="I231" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10821,10 +10864,10 @@
         <v>4</v>
       </c>
       <c r="H234" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I234" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I234" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10850,10 +10893,10 @@
         <v>4</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I235" s="2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11333,8 +11376,8 @@
       <c r="D252" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E252" s="2" t="s">
-        <v>40</v>
+      <c r="E252" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>14</v>
@@ -11897,7 +11940,7 @@
         <v>45</v>
       </c>
       <c r="I271" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12245,7 +12288,7 @@
         <v>30</v>
       </c>
       <c r="I283" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12299,6 +12342,12 @@
       <c r="G285" s="2">
         <v>2</v>
       </c>
+      <c r="H285" t="s">
+        <v>106</v>
+      </c>
+      <c r="I285" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="286" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
@@ -12703,7 +12752,7 @@
         <v>45</v>
       </c>
       <c r="I299" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13183,8 +13232,8 @@
       <c r="D316" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E316" s="2" t="s">
-        <v>60</v>
+      <c r="E316" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>32</v>
@@ -13457,7 +13506,7 @@
         <v>45</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="326" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13486,7 +13535,7 @@
         <v>45</v>
       </c>
       <c r="I326" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="327" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13805,7 +13854,7 @@
         <v>16</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="338" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14791,7 +14840,7 @@
         <v>35</v>
       </c>
       <c r="I371" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="372" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14878,7 +14927,7 @@
         <v>30</v>
       </c>
       <c r="I374" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="375" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15313,7 +15362,7 @@
         <v>16</v>
       </c>
       <c r="I389" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="390" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15748,7 +15797,7 @@
         <v>30</v>
       </c>
       <c r="I404" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="405" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16038,7 +16087,7 @@
         <v>30</v>
       </c>
       <c r="I414" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="415" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16241,7 +16290,7 @@
         <v>30</v>
       </c>
       <c r="I421" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="422" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16473,7 +16522,7 @@
         <v>30</v>
       </c>
       <c r="I429" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="430" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16618,7 +16667,7 @@
         <v>30</v>
       </c>
       <c r="I434" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="435" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16647,7 +16696,7 @@
         <v>30</v>
       </c>
       <c r="I435" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="436" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16763,7 +16812,7 @@
         <v>30</v>
       </c>
       <c r="I439" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="440" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16879,7 +16928,7 @@
         <v>30</v>
       </c>
       <c r="I443" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="444" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17082,7 +17131,7 @@
         <v>35</v>
       </c>
       <c r="I450" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="451" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17488,7 +17537,7 @@
         <v>16</v>
       </c>
       <c r="I464" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="465" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17719,6 +17768,9 @@
       <c r="H472" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I472" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="473" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
@@ -18877,7 +18929,7 @@
         <v>45</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="513" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19718,7 +19770,7 @@
         <v>33</v>
       </c>
       <c r="I541" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="542" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19747,7 +19799,7 @@
         <v>33</v>
       </c>
       <c r="I542" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="543" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20878,7 +20930,7 @@
         <v>33</v>
       </c>
       <c r="I581" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="582" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21168,7 +21220,7 @@
         <v>33</v>
       </c>
       <c r="I591" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="592" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21806,7 +21858,7 @@
         <v>30</v>
       </c>
       <c r="I613" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="614" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22821,7 +22873,7 @@
         <v>45</v>
       </c>
       <c r="I648" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="649" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22866,8 +22918,8 @@
       <c r="D650" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E650" s="2" t="s">
-        <v>16</v>
+      <c r="E650" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="F650" s="2" t="s">
         <v>32</v>
@@ -23098,8 +23150,8 @@
       <c r="D658" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E658" s="2" t="s">
-        <v>60</v>
+      <c r="E658" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="F658" s="2" t="s">
         <v>14</v>
@@ -23446,8 +23498,8 @@
       <c r="D670" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E670" s="2" t="s">
-        <v>16</v>
+      <c r="E670" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="F670" s="2" t="s">
         <v>32</v>
@@ -23630,7 +23682,7 @@
         <v>4</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="I676" s="2" t="s">
         <v>17</v>
@@ -24519,8 +24571,8 @@
       <c r="D707" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E707" s="2" t="s">
-        <v>16</v>
+      <c r="E707" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="F707" s="2" t="s">
         <v>14</v>
@@ -30125,6 +30177,9 @@
       <c r="G900" s="2">
         <v>7</v>
       </c>
+      <c r="H900" t="s">
+        <v>17</v>
+      </c>
       <c r="I900" s="2" t="s">
         <v>17</v>
       </c>
@@ -34244,7 +34299,7 @@
         <v>60</v>
       </c>
       <c r="I1042" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1043" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -36155,7 +36210,7 @@
         <v>23</v>
       </c>
       <c r="H1108" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I1108" s="2" t="s">
         <v>17</v>
